--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2020_tarapaca.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2020_tarapaca.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:41</t>
+    <t xml:space="preserve">2026-10-05 02:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>314343.81</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -844,10 +844,10 @@
         <v>16</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>323553.12</v>
+        <v>323553.13</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -866,7 +866,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>340653.12</v>
+        <v>340653.13</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>332189.75</v>
@@ -913,7 +913,7 @@
         <v>339944.91</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -954,7 +954,7 @@
         <v>26</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>375047.12</v>
+        <v>375047.13</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>363139.97</v>
@@ -1020,7 +1020,7 @@
         <v>32</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>309080.62</v>
+        <v>309080.63</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>304271.59</v>
@@ -1031,7 +1031,7 @@
         <v>33</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>310412.12</v>
+        <v>310412.13</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>305187.22</v>
@@ -1273,7 +1273,7 @@
         <v>55</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>388456.62</v>
+        <v>388456.63</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>388053</v>
@@ -1287,7 +1287,7 @@
         <v>397577.28</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1372,7 +1372,7 @@
         <v>64</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>427213.62</v>
+        <v>427213.63</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>422267.97</v>
@@ -1529,7 +1529,7 @@
         <v>457741.47</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1595,7 +1595,7 @@
         <v>475355.47</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
